--- a/template.xlsx
+++ b/template.xlsx
@@ -3,15 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="현재_통합_문서" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E511F210-86D2-4420-87EA-8A774EF05F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F171F4-38A2-482A-90BF-9FE9B0C59C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33285" yWindow="2295" windowWidth="18930" windowHeight="11775" xr2:uid="{86590153-3C62-4454-9904-9A161584E993}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{86590153-3C62-4454-9904-9A161584E993}"/>
   </bookViews>
   <sheets>
     <sheet name="1안" sheetId="74" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="75" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1안'!$A$18:$M$236</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$H$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'1안'!$A$1:$N$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -19,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="113">
   <si>
     <t>성명</t>
   </si>
@@ -479,13 +481,36 @@
     <t xml:space="preserve">Positive or Negative_x000D_
 </t>
   </si>
+  <si>
+    <t>회사/기관명</t>
+  </si>
+  <si>
+    <t>평가사구분</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>유효기간</t>
+  </si>
+  <si>
+    <t>현장평가</t>
+  </si>
+  <si>
+    <t>평가점수</t>
+  </si>
+  <si>
+    <t>순위</t>
+  </si>
+  <si>
+    <t>비고</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="&quot;,&quot;General"/>
+    <numFmt numFmtId="177" formatCode="yyyy/mm/dd;@"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -800,7 +825,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -941,6 +966,9 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -954,7 +982,57 @@
     <cellStyle name="표준 7" xfId="9" xr:uid="{B81D10E5-E58D-4524-B323-E5B6085520BE}"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1129,13 +1207,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -1179,13 +1257,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -1229,13 +1307,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -1279,13 +1357,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -1329,13 +1407,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -1379,13 +1457,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -1429,13 +1507,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -1479,13 +1557,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -1529,13 +1607,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -1579,13 +1657,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -1629,13 +1707,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -1679,13 +1757,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -1729,13 +1807,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -1779,13 +1857,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -1829,13 +1907,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -1879,13 +1957,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -1929,13 +2007,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -1979,13 +2057,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -2029,13 +2107,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -2079,13 +2157,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -2129,13 +2207,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -2179,13 +2257,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -2229,13 +2307,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -2279,13 +2357,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>2721</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>164646</xdr:rowOff>
         </xdr:to>
@@ -2329,13 +2407,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>145596</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>4</xdr:row>
           <xdr:rowOff>62593</xdr:rowOff>
         </xdr:to>
@@ -2379,13 +2457,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>145596</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>4</xdr:row>
           <xdr:rowOff>62593</xdr:rowOff>
         </xdr:to>
@@ -2429,13 +2507,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>145596</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>4</xdr:row>
           <xdr:rowOff>62593</xdr:rowOff>
         </xdr:to>
@@ -2479,13 +2557,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>145596</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>4</xdr:row>
           <xdr:rowOff>62593</xdr:rowOff>
         </xdr:to>
@@ -2529,13 +2607,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>145596</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>4</xdr:row>
           <xdr:rowOff>62593</xdr:rowOff>
         </xdr:to>
@@ -2579,13 +2657,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>145596</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>4</xdr:row>
           <xdr:rowOff>62593</xdr:rowOff>
         </xdr:to>
@@ -2629,13 +2707,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>145596</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>4</xdr:row>
           <xdr:rowOff>62593</xdr:rowOff>
         </xdr:to>
@@ -2679,13 +2757,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>327932</xdr:colOff>
+          <xdr:colOff>337457</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>145596</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>966107</xdr:colOff>
+          <xdr:colOff>975632</xdr:colOff>
           <xdr:row>4</xdr:row>
           <xdr:rowOff>62593</xdr:rowOff>
         </xdr:to>
@@ -19840,13 +19918,13 @@
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="B4:N6 C10:C11">
-    <cfRule type="duplicateValues" dxfId="2" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:N6">
-    <cfRule type="duplicateValues" dxfId="1" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="74"/>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3" xr:uid="{B4CB36EF-3517-41C4-8535-D623748B8D4B}">
@@ -19866,18 +19944,218 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19457" r:id="rId5" name="Control 1">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId6">
+        <control shapeId="19488" r:id="rId5" name="Control 32">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>142875</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>971550</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="19488" r:id="rId5" name="Control 32"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="19487" r:id="rId7" name="Control 31">
+          <controlPr defaultSize="0" r:id="rId8">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>333375</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>142875</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>971550</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="19487" r:id="rId7" name="Control 31"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="19486" r:id="rId9" name="Control 30">
+          <controlPr defaultSize="0" r:id="rId6">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>333375</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>142875</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>971550</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="19486" r:id="rId9" name="Control 30"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="19485" r:id="rId10" name="Control 29">
+          <controlPr defaultSize="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>333375</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>142875</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>971550</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="19485" r:id="rId10" name="Control 29"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="19484" r:id="rId12" name="Control 28">
+          <controlPr defaultSize="0" r:id="rId6">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>333375</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>142875</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>971550</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="19484" r:id="rId12" name="Control 28"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="19483" r:id="rId13" name="Control 27">
+          <controlPr defaultSize="0" r:id="rId14">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>333375</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>142875</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>971550</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="19483" r:id="rId13" name="Control 27"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="19482" r:id="rId15" name="Control 26">
+          <controlPr defaultSize="0" r:id="rId6">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>333375</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>142875</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>971550</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="19482" r:id="rId15" name="Control 26"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="19481" r:id="rId16" name="Control 25">
+          <controlPr defaultSize="0" r:id="rId17">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>333375</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>142875</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>971550</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="19481" r:id="rId16" name="Control 25"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="19480" r:id="rId18" name="Control 24">
+          <controlPr defaultSize="0" r:id="rId19">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -19886,23 +20164,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19457" r:id="rId5" name="Control 1"/>
+        <control shapeId="19480" r:id="rId18" name="Control 24"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19458" r:id="rId7" name="Control 2">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId8">
+        <control shapeId="19479" r:id="rId20" name="Control 23">
+          <controlPr defaultSize="0" r:id="rId21">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -19911,23 +20189,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19458" r:id="rId7" name="Control 2"/>
+        <control shapeId="19479" r:id="rId20" name="Control 23"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19459" r:id="rId9" name="Control 3">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId10">
+        <control shapeId="19478" r:id="rId22" name="Control 22">
+          <controlPr defaultSize="0" r:id="rId23">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -19936,23 +20214,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19459" r:id="rId9" name="Control 3"/>
+        <control shapeId="19478" r:id="rId22" name="Control 22"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19460" r:id="rId11" name="Control 4">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId8">
+        <control shapeId="19477" r:id="rId24" name="Control 21">
+          <controlPr defaultSize="0" r:id="rId25">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -19961,23 +20239,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19460" r:id="rId11" name="Control 4"/>
+        <control shapeId="19477" r:id="rId24" name="Control 21"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19461" r:id="rId12" name="Control 5">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId13">
+        <control shapeId="19476" r:id="rId26" name="Control 20">
+          <controlPr defaultSize="0" r:id="rId27">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -19986,23 +20264,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19461" r:id="rId12" name="Control 5"/>
+        <control shapeId="19476" r:id="rId26" name="Control 20"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19462" r:id="rId14" name="Control 6">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId8">
+        <control shapeId="19475" r:id="rId28" name="Control 19">
+          <controlPr defaultSize="0" r:id="rId29">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -20011,23 +20289,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19462" r:id="rId14" name="Control 6"/>
+        <control shapeId="19475" r:id="rId28" name="Control 19"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19463" r:id="rId15" name="Control 7">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId16">
+        <control shapeId="19474" r:id="rId30" name="Control 18">
+          <controlPr defaultSize="0" r:id="rId31">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -20036,23 +20314,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19463" r:id="rId15" name="Control 7"/>
+        <control shapeId="19474" r:id="rId30" name="Control 18"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19464" r:id="rId17" name="Control 8">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId8">
+        <control shapeId="19473" r:id="rId32" name="Control 17">
+          <controlPr defaultSize="0" r:id="rId33">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -20061,23 +20339,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19464" r:id="rId17" name="Control 8"/>
+        <control shapeId="19473" r:id="rId32" name="Control 17"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19465" r:id="rId18" name="Control 9">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId19">
+        <control shapeId="19472" r:id="rId34" name="Control 16">
+          <controlPr defaultSize="0" r:id="rId19">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -20086,23 +20364,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19465" r:id="rId18" name="Control 9"/>
+        <control shapeId="19472" r:id="rId34" name="Control 16"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19466" r:id="rId20" name="Control 10">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId8">
+        <control shapeId="19471" r:id="rId35" name="Control 15">
+          <controlPr defaultSize="0" r:id="rId36">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -20111,23 +20389,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19466" r:id="rId20" name="Control 10"/>
+        <control shapeId="19471" r:id="rId35" name="Control 15"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19467" r:id="rId21" name="Control 11">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId22">
+        <control shapeId="19470" r:id="rId37" name="Control 14">
+          <controlPr defaultSize="0" r:id="rId19">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -20136,23 +20414,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19467" r:id="rId21" name="Control 11"/>
+        <control shapeId="19470" r:id="rId37" name="Control 14"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19468" r:id="rId23" name="Control 12">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId8">
+        <control shapeId="19469" r:id="rId38" name="Control 13">
+          <controlPr defaultSize="0" r:id="rId39">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -20161,23 +20439,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19468" r:id="rId23" name="Control 12"/>
+        <control shapeId="19469" r:id="rId38" name="Control 13"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19469" r:id="rId24" name="Control 13">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId25">
+        <control shapeId="19468" r:id="rId40" name="Control 12">
+          <controlPr defaultSize="0" r:id="rId19">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -20186,23 +20464,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19469" r:id="rId24" name="Control 13"/>
+        <control shapeId="19468" r:id="rId40" name="Control 12"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19470" r:id="rId26" name="Control 14">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId8">
+        <control shapeId="19467" r:id="rId41" name="Control 11">
+          <controlPr defaultSize="0" r:id="rId42">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -20211,23 +20489,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19470" r:id="rId26" name="Control 14"/>
+        <control shapeId="19467" r:id="rId41" name="Control 11"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19471" r:id="rId27" name="Control 15">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId28">
+        <control shapeId="19466" r:id="rId43" name="Control 10">
+          <controlPr defaultSize="0" r:id="rId19">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -20236,23 +20514,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19471" r:id="rId27" name="Control 15"/>
+        <control shapeId="19466" r:id="rId43" name="Control 10"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19472" r:id="rId29" name="Control 16">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId8">
+        <control shapeId="19465" r:id="rId44" name="Control 9">
+          <controlPr defaultSize="0" r:id="rId45">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -20261,23 +20539,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19472" r:id="rId29" name="Control 16"/>
+        <control shapeId="19465" r:id="rId44" name="Control 9"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19473" r:id="rId30" name="Control 17">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId31">
+        <control shapeId="19464" r:id="rId46" name="Control 8">
+          <controlPr defaultSize="0" r:id="rId19">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -20286,23 +20564,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19473" r:id="rId30" name="Control 17"/>
+        <control shapeId="19464" r:id="rId46" name="Control 8"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19474" r:id="rId32" name="Control 18">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId33">
+        <control shapeId="19463" r:id="rId47" name="Control 7">
+          <controlPr defaultSize="0" r:id="rId48">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -20311,23 +20589,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19474" r:id="rId32" name="Control 18"/>
+        <control shapeId="19463" r:id="rId47" name="Control 7"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19475" r:id="rId34" name="Control 19">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId35">
+        <control shapeId="19462" r:id="rId49" name="Control 6">
+          <controlPr defaultSize="0" r:id="rId19">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -20336,23 +20614,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19475" r:id="rId34" name="Control 19"/>
+        <control shapeId="19462" r:id="rId49" name="Control 6"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19476" r:id="rId36" name="Control 20">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId37">
+        <control shapeId="19461" r:id="rId50" name="Control 5">
+          <controlPr defaultSize="0" r:id="rId51">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -20361,23 +20639,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19476" r:id="rId36" name="Control 20"/>
+        <control shapeId="19461" r:id="rId50" name="Control 5"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19477" r:id="rId38" name="Control 21">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId39">
+        <control shapeId="19460" r:id="rId52" name="Control 4">
+          <controlPr defaultSize="0" r:id="rId19">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -20386,23 +20664,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19477" r:id="rId38" name="Control 21"/>
+        <control shapeId="19460" r:id="rId52" name="Control 4"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19478" r:id="rId40" name="Control 22">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId41">
+        <control shapeId="19459" r:id="rId53" name="Control 3">
+          <controlPr defaultSize="0" r:id="rId54">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -20411,23 +20689,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19478" r:id="rId40" name="Control 22"/>
+        <control shapeId="19459" r:id="rId53" name="Control 3"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19479" r:id="rId42" name="Control 23">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId43">
+        <control shapeId="19458" r:id="rId55" name="Control 2">
+          <controlPr defaultSize="0" r:id="rId19">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -20436,23 +20714,23 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19479" r:id="rId42" name="Control 23"/>
+        <control shapeId="19458" r:id="rId55" name="Control 2"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="19480" r:id="rId44" name="Control 24">
-          <controlPr defaultSize="0" autoPict="0" r:id="rId8">
+        <control shapeId="19457" r:id="rId56" name="Control 1">
+          <controlPr defaultSize="0" r:id="rId57">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
+                <xdr:colOff>333375</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
+                <xdr:colOff>971550</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </to>
@@ -20461,209 +20739,65 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="19480" r:id="rId44" name="Control 24"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="19481" r:id="rId45" name="Control 25">
-          <controlPr defaultSize="0" r:id="rId46">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>142875</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="19481" r:id="rId45" name="Control 25"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="19482" r:id="rId47" name="Control 26">
-          <controlPr defaultSize="0" r:id="rId48">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>142875</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="19482" r:id="rId47" name="Control 26"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="19483" r:id="rId49" name="Control 27">
-          <controlPr defaultSize="0" r:id="rId50">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>142875</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="19483" r:id="rId49" name="Control 27"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="19484" r:id="rId51" name="Control 28">
-          <controlPr defaultSize="0" r:id="rId48">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>142875</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="19484" r:id="rId51" name="Control 28"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="19485" r:id="rId52" name="Control 29">
-          <controlPr defaultSize="0" r:id="rId53">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>142875</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="19485" r:id="rId52" name="Control 29"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="19486" r:id="rId54" name="Control 30">
-          <controlPr defaultSize="0" r:id="rId48">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>142875</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="19486" r:id="rId54" name="Control 30"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="19487" r:id="rId55" name="Control 31">
-          <controlPr defaultSize="0" r:id="rId56">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>142875</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="19487" r:id="rId55" name="Control 31"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="19488" r:id="rId57" name="Control 32">
-          <controlPr defaultSize="0" r:id="rId48">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>323850</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>142875</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>962025</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="19488" r:id="rId57" name="Control 32"/>
+        <control shapeId="19457" r:id="rId56" name="Control 1"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B10D2E4-2685-48CA-9E72-C9EE1C7A2B78}">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="3" max="3" width="13.75" customWidth="1"/>
+    <col min="4" max="4" width="10.75" customWidth="1"/>
+    <col min="5" max="5" width="13.5" customWidth="1"/>
+    <col min="6" max="6" width="11.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="17.25">
+      <c r="A1" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="H1" s="50" t="s">
+        <v>112</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H1" xr:uid="{1B10D2E4-2685-48CA-9E72-C9EE1C7A2B78}"/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="B1">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1">
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>